--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Май 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Май 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92555672264</v>
+        <v>46157.9311352045</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Май 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Май 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9311352045</v>
+        <v>46157.93137076075</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Май 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Май 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93137076075</v>
+        <v>46157.93384474608</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Май 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Май 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93384474608</v>
+        <v>46157.93696267096</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Май 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Май 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93696267096</v>
+        <v>46158.2820519331</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Май 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Май 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2820519331</v>
+        <v>46158.29652958898</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Май 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Май 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29652958898</v>
+        <v>46158.29808103071</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Май 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Май 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29808103071</v>
+        <v>46158.33370868921</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Май 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Май 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33370868921</v>
+        <v>46158.37222061717</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Май 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Май 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37222061717</v>
+        <v>46158.37275864036</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
